--- a/output/2026-10-11_19_Serbia_Borski_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-11_19_Serbia_Borski_Utensilerie_e_Macchine_Utensili.xlsx
@@ -474,7 +474,6 @@
           <t>Woby Haus - prodaja mašina i alata</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Bor, Borski okrug</t>
@@ -490,10 +489,9 @@
           <t>030/2150-020</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Punto vendita confermato esistente (Nikole Pašića 21, Bor) tramite PlanPlus e Wolt, vende trapani/pialle elettriche ecc. Nessuna evidenza di attività all'ingrosso/B2B: il canale Wolt lo presenta come rivolto a hobbisti/artigiani, non a imprese. Numero alternativo reperito online: +381 63 236 255 (Wolt). Natura B2B da confermare con contatto diretto.</t>
+          <t>Punto vendita confermato esistente (Nikole Pašića 21, Bor) tramite PlanPlus e Wolt, vende trapani/pialle elettriche ecc. Nessuna evidenza di attività all'ingrosso/B2B: il canale Wolt lo presenta come rivolto a hobbisti/artigiani, non a imprese. Numero alternativo reperito online: +381 63 236 255 (Wolt). Natura B2B da confermare con contatto diretto. [DUPLICATO — vedi anche: 2026-10-08_01_Serbia_Kolubarski_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
